--- a/data/vendor-search/results_all_smartplugs.xlsx
+++ b/data/vendor-search/results_all_smartplugs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>cpe_strings</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>matched_terms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -472,8 +477,10 @@
       <c r="D2" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E2" t="n">
-        <v>3</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -483,6 +490,11 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>cpe:2.3:o:meross:mss110_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:meross:mss110:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>meross</t>
         </is>
       </c>
     </row>
@@ -505,8 +517,10 @@
       <c r="D3" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E3" t="n">
-        <v>3</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -516,6 +530,11 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>cpe:2.3:o:meross:mss110_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:meross:mss110:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>meross</t>
         </is>
       </c>
     </row>
@@ -538,8 +557,10 @@
       <c r="D4" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E4" t="n">
-        <v>3</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -549,6 +570,11 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>cpe:2.3:o:belkin:crock-pot_smart_slow_cooker_with_wemo_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:belkin:crock-pot_smart_slow_cooker_with_wemo:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>wemo|belkin wemo</t>
         </is>
       </c>
     </row>
@@ -571,8 +597,10 @@
       <c r="D5" t="n">
         <v>4.8</v>
       </c>
-      <c r="E5" t="n">
-        <v>3.1</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -582,6 +610,11 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>cpe:2.3:o:sonoff:th10_firmware:6.6.0.21:*:*:*:*:*:*:*|cpe:2.3:h:sonoff:th10:-:*:*:*:*:*:*:*|cpe:2.3:o:sonoff:th16_firmware:6.6.0.21:*:*:*:*:*:*:*|cpe:2.3:h:sonoff:th16:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>sonoff</t>
         </is>
       </c>
     </row>
@@ -604,8 +637,10 @@
       <c r="D6" t="n">
         <v>7.8</v>
       </c>
-      <c r="E6" t="n">
-        <v>3.1</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -615,6 +650,11 @@
       <c r="G6" t="inlineStr">
         <is>
           <t>cpe:2.3:o:belkin:wemo_insight_switch_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:belkin:wemo_insight_switch:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>wemo|belkin wemo</t>
         </is>
       </c>
     </row>
@@ -637,8 +677,10 @@
       <c r="D7" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E7" t="n">
-        <v>3.1</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -648,6 +690,11 @@
       <c r="G7" t="inlineStr">
         <is>
           <t>cpe:2.3:o:belkin:wemo_switch_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:belkin:wemo_switch:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>wemo|belkin wemo</t>
         </is>
       </c>
     </row>
@@ -670,8 +717,10 @@
       <c r="D8" t="n">
         <v>8.1</v>
       </c>
-      <c r="E8" t="n">
-        <v>3.1</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -681,6 +730,11 @@
       <c r="G8" t="inlineStr">
         <is>
           <t>cpe:2.3:o:meross:msg100_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:meross:msg100:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>meross</t>
         </is>
       </c>
     </row>
@@ -703,8 +757,10 @@
       <c r="D9" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="n">
-        <v>3.1</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -714,6 +770,11 @@
       <c r="G9" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.6.9h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>anker eufy</t>
         </is>
       </c>
     </row>
@@ -736,8 +797,10 @@
       <c r="D10" t="n">
         <v>9</v>
       </c>
-      <c r="E10" t="n">
-        <v>3.1</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -747,6 +810,11 @@
       <c r="G10" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.6.9h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>anker eufy</t>
         </is>
       </c>
     </row>
@@ -769,8 +837,10 @@
       <c r="D11" t="n">
         <v>6.5</v>
       </c>
-      <c r="E11" t="n">
-        <v>3.1</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -780,6 +850,11 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>cpe:2.3:o:meross:mss550x_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:meross:mss550x:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>meross</t>
         </is>
       </c>
     </row>
@@ -802,8 +877,10 @@
       <c r="D12" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E12" t="n">
-        <v>3.1</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -813,6 +890,11 @@
       <c r="G12" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.8.5h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>anker eufy</t>
         </is>
       </c>
     </row>
@@ -835,8 +917,10 @@
       <c r="D13" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E13" t="n">
-        <v>3.1</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -846,6 +930,11 @@
       <c r="G13" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.8.5h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>anker eufy</t>
         </is>
       </c>
     </row>
@@ -868,8 +957,10 @@
       <c r="D14" t="n">
         <v>6.5</v>
       </c>
-      <c r="E14" t="n">
-        <v>3.1</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -879,6 +970,11 @@
       <c r="G14" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.8.5h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>anker eufy</t>
         </is>
       </c>
     </row>
@@ -901,8 +997,10 @@
       <c r="D15" t="n">
         <v>6.4</v>
       </c>
-      <c r="E15" t="n">
-        <v>3.1</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -912,6 +1010,11 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tapo_c200_v1_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_c200_v1:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
         </is>
       </c>
     </row>
@@ -934,8 +1037,10 @@
       <c r="D16" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E16" t="n">
-        <v>3.1</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -945,6 +1050,11 @@
       <c r="G16" t="inlineStr">
         <is>
           <t>cpe:2.3:o:belkin:f7c063_firmware:2.00.11420.owrt.pvt_snsv2:*:*:*:*:*:*:*|cpe:2.3:h:belkin:f7c063:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>smart outlet</t>
         </is>
       </c>
     </row>
@@ -967,8 +1077,10 @@
       <c r="D17" t="n">
         <v>7.5</v>
       </c>
-      <c r="E17" t="n">
-        <v>3.1</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -978,6 +1090,11 @@
       <c r="G17" t="inlineStr">
         <is>
           <t>cpe:2.3:o:blitzwolf:bw-is22_firmware:1.0:*:*:*:*:*:*:*|cpe:2.3:h:blitzwolf:bw-is22:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>blitzwolf</t>
         </is>
       </c>
     </row>
@@ -1000,8 +1117,10 @@
       <c r="D18" t="n">
         <v>7.5</v>
       </c>
-      <c r="E18" t="n">
-        <v>3.1</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
@@ -1009,6 +1128,11 @@
           <t>cpe:2.3:o:tp-link:tapo_l530e_firmware:1.0.0:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_l530e:-:*:*:*:*:*:*:*|cpe:2.3:a:tp-link:tapo:2.8.14:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>tplink</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1029,8 +1153,10 @@
       <c r="D19" t="n">
         <v>6.3</v>
       </c>
-      <c r="E19" t="n">
-        <v>3.1</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1038,6 +1164,11 @@
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1058,8 +1189,10 @@
       <c r="D20" t="n">
         <v>7.6</v>
       </c>
-      <c r="E20" t="n">
-        <v>3.1</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1067,6 +1200,11 @@
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>tp-link kasa</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1087,8 +1225,10 @@
       <c r="D21" t="n">
         <v>4.3</v>
       </c>
-      <c r="E21" t="n">
-        <v>3.1</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1096,6 +1236,11 @@
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>tp-link kasa</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1116,8 +1261,10 @@
       <c r="D22" t="n">
         <v>7.8</v>
       </c>
-      <c r="E22" t="n">
-        <v>2</v>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1127,6 +1274,11 @@
       <c r="G22" t="inlineStr">
         <is>
           <t>cpe:2.3:a:belkin:wemo_home_automation_firmware:2769:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>wemo|belkin wemo</t>
         </is>
       </c>
     </row>
@@ -1149,8 +1301,10 @@
       <c r="D23" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="E23" t="n">
-        <v>2</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1160,6 +1314,11 @@
       <c r="G23" t="inlineStr">
         <is>
           <t>cpe:2.3:a:belkin:wemo_home_automation_firmware:2769:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>wemo|belkin wemo</t>
         </is>
       </c>
     </row>
@@ -1182,8 +1341,10 @@
       <c r="D24" t="n">
         <v>7.8</v>
       </c>
-      <c r="E24" t="n">
-        <v>2</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1193,6 +1354,11 @@
       <c r="G24" t="inlineStr">
         <is>
           <t>cpe:2.3:a:belkin:wemo_home_automation_firmware:2769:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>wemo|belkin wemo</t>
         </is>
       </c>
     </row>
@@ -1215,8 +1381,10 @@
       <c r="D25" t="n">
         <v>7.1</v>
       </c>
-      <c r="E25" t="n">
-        <v>2</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1226,6 +1394,11 @@
       <c r="G25" t="inlineStr">
         <is>
           <t>cpe:2.3:a:belkin:wemo_home_automation_firmware:2769:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>wemo|belkin wemo</t>
         </is>
       </c>
     </row>
@@ -1248,8 +1421,10 @@
       <c r="D26" t="n">
         <v>10</v>
       </c>
-      <c r="E26" t="n">
-        <v>2</v>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1259,6 +1434,11 @@
       <c r="G26" t="inlineStr">
         <is>
           <t>cpe:2.3:a:belkin:wemo_home_automation_firmware:2769:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>wemo|belkin wemo</t>
         </is>
       </c>
     </row>
@@ -1281,8 +1461,10 @@
       <c r="D27" t="n">
         <v>6.8</v>
       </c>
-      <c r="E27" t="n">
-        <v>2</v>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1292,6 +1474,11 @@
       <c r="G27" t="inlineStr">
         <is>
           <t>cpe:2.3:h:kankun:smartsocket:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>smart socket</t>
         </is>
       </c>
     </row>
@@ -1314,8 +1501,10 @@
       <c r="D28" t="n">
         <v>10</v>
       </c>
-      <c r="E28" t="n">
-        <v>3.1</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1325,6 +1514,11 @@
       <c r="G28" t="inlineStr">
         <is>
           <t>cpe:2.3:o:belkin:wemo_insight_smart_plug_firmware:-:*:*:*:*:*:*:*|cpe:2.3:h:belkin:wemo_insight_smart_plug:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>wemo|belkin wemo</t>
         </is>
       </c>
     </row>
@@ -1347,8 +1541,10 @@
       <c r="D29" t="n">
         <v>7.5</v>
       </c>
-      <c r="E29" t="n">
-        <v>3.1</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1358,6 +1554,11 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>cpe:2.3:o:belkin:wemo_switch_28b_firmware:wemo_ww_2.00.11057.pvt-owrt-sns:*:*:*:*:*:*:*|cpe:2.3:h:belkin:wemo_switch_28b:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>wemo|belkin wemo</t>
         </is>
       </c>
     </row>
@@ -1380,8 +1581,10 @@
       <c r="D30" t="n">
         <v>5.5</v>
       </c>
-      <c r="E30" t="n">
-        <v>3.1</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1391,6 +1594,11 @@
       <c r="G30" t="inlineStr">
         <is>
           <t>cpe:2.3:a:tp-link:omada_controller:3.2.6:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>tplink</t>
         </is>
       </c>
     </row>
@@ -1413,8 +1621,10 @@
       <c r="D31" t="n">
         <v>5</v>
       </c>
-      <c r="E31" t="n">
-        <v>3.1</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1424,6 +1634,11 @@
       <c r="G31" t="inlineStr">
         <is>
           <t>cpe:2.3:a:openhab:openhab:*:*:*:*:*:*:*:*|cpe:2.3:a:openhab:openhab:3.0.0:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>wemo</t>
         </is>
       </c>
     </row>
@@ -1446,8 +1661,10 @@
       <c r="D32" t="n">
         <v>10</v>
       </c>
-      <c r="E32" t="n">
-        <v>3.1</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1457,6 +1674,11 @@
       <c r="G32" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.6.9h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>anker eufy</t>
         </is>
       </c>
     </row>
@@ -1479,8 +1701,10 @@
       <c r="D33" t="n">
         <v>10</v>
       </c>
-      <c r="E33" t="n">
-        <v>3.1</v>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1490,6 +1714,11 @@
       <c r="G33" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.6.9h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>anker eufy</t>
         </is>
       </c>
     </row>
@@ -1512,8 +1741,10 @@
       <c r="D34" t="n">
         <v>9.9</v>
       </c>
-      <c r="E34" t="n">
-        <v>3.1</v>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -1523,6 +1754,11 @@
       <c r="G34" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.6.9h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>anker eufy</t>
         </is>
       </c>
     </row>
@@ -1545,8 +1781,10 @@
       <c r="D35" t="n">
         <v>7.5</v>
       </c>
-      <c r="E35" t="n">
-        <v>3.1</v>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -1556,6 +1794,11 @@
       <c r="G35" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.6.9h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>anker eufy</t>
         </is>
       </c>
     </row>
@@ -1578,8 +1821,10 @@
       <c r="D36" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E36" t="n">
-        <v>3.1</v>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -1589,6 +1834,11 @@
       <c r="G36" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.6.9h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>anker eufy</t>
         </is>
       </c>
     </row>
@@ -1611,8 +1861,10 @@
       <c r="D37" t="n">
         <v>8.1</v>
       </c>
-      <c r="E37" t="n">
-        <v>3.1</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -1622,6 +1874,11 @@
       <c r="G37" t="inlineStr">
         <is>
           <t>cpe:2.3:o:anker:eufy_homebase_2_firmware:2.1.6.9h:*:*:*:*:*:*:*|cpe:2.3:h:anker:eufy_homebase_2:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>anker eufy</t>
         </is>
       </c>
     </row>
@@ -1644,8 +1901,10 @@
       <c r="D38" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="E38" t="n">
-        <v>3.1</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1655,6 +1914,11 @@
       <c r="G38" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tapo_c200_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_c200:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
         </is>
       </c>
     </row>
@@ -1677,8 +1941,10 @@
       <c r="D39" t="n">
         <v>7.5</v>
       </c>
-      <c r="E39" t="n">
-        <v>3.1</v>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1688,6 +1954,11 @@
       <c r="G39" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tapo_c310_firmware:1.3.0:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_c310:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
         </is>
       </c>
     </row>
@@ -1710,8 +1981,10 @@
       <c r="D40" t="n">
         <v>4.6</v>
       </c>
-      <c r="E40" t="n">
-        <v>3.1</v>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1721,6 +1994,11 @@
       <c r="G40" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tapo_c200_firmware:1.2.2:build_220725:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_c200:3:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
         </is>
       </c>
     </row>
@@ -1743,8 +2021,10 @@
       <c r="D41" t="n">
         <v>4.6</v>
       </c>
-      <c r="E41" t="n">
-        <v>3.1</v>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1754,6 +2034,11 @@
       <c r="G41" t="inlineStr">
         <is>
           <t>cpe:2.3:o:etekcity:3-in-1_smart_door_lock_firmware:1.0:*:*:*:*:*:*:*|cpe:2.3:h:etekcity:3-in-1_smart_door_lock:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>etekcity</t>
         </is>
       </c>
     </row>
@@ -1776,8 +2061,10 @@
       <c r="D42" t="n">
         <v>6.5</v>
       </c>
-      <c r="E42" t="n">
-        <v>3.1</v>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
@@ -1785,6 +2072,11 @@
           <t>cpe:2.3:a:tp-link:tapo:2.8.14:*:*:*:*:*:*:*|cpe:2.3:o:tp-link:tapo_l530e_firmware:1.0.0:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_l530e:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>tplink</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1805,8 +2097,10 @@
       <c r="D43" t="n">
         <v>6.5</v>
       </c>
-      <c r="E43" t="n">
-        <v>3.1</v>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
@@ -1814,6 +2108,11 @@
           <t>cpe:2.3:a:tp-link:tapo:2.8.14:*:*:*:*:*:*:*|cpe:2.3:o:tp-link:tapo_l530e_firmware:1.0.0:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_l530e:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>tplink</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1834,8 +2133,10 @@
       <c r="D44" t="n">
         <v>6.5</v>
       </c>
-      <c r="E44" t="n">
-        <v>3.1</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
@@ -1843,6 +2144,11 @@
           <t>cpe:2.3:a:tp-link:tapo:2.8.14:*:*:*:*:*:*:*|cpe:2.3:o:tp-link:tapo_l530e_firmware:1.0.0:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_l530e:-:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>tplink</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1863,8 +2169,10 @@
       <c r="D45" t="n">
         <v>6.5</v>
       </c>
-      <c r="E45" t="n">
-        <v>3.1</v>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1874,6 +2182,11 @@
       <c r="G45" t="inlineStr">
         <is>
           <t>cpe:2.3:o:belkin:wemo_smart_plug_wsp080_firmware:1.2:*:*:*:*:*:*:*|cpe:2.3:h:belkin:wemo_smart_plug_wsp080:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>wemo|belkin wemo</t>
         </is>
       </c>
     </row>
@@ -1896,8 +2209,10 @@
       <c r="D46" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E46" t="n">
-        <v>3.1</v>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1907,6 +2222,11 @@
       <c r="G46" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tl-er5120g_firmware:2.0.0:build_210817:*:*:*:*:*:*|cpe:2.3:h:tp-link:tl-er5120g:4.0:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>tplink</t>
         </is>
       </c>
     </row>
@@ -1929,8 +2249,10 @@
       <c r="D47" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E47" t="n">
-        <v>3.1</v>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1940,6 +2262,11 @@
       <c r="G47" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tl-er5120g_firmware:2.0.0:build_210817:*:*:*:*:*:*|cpe:2.3:h:tp-link:tl-er5120g:4.0:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>tplink</t>
         </is>
       </c>
     </row>
@@ -1962,8 +2289,10 @@
       <c r="D48" t="n">
         <v>6.5</v>
       </c>
-      <c r="E48" t="n">
-        <v>3.1</v>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1973,6 +2302,11 @@
       <c r="G48" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tapo_c100_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_c100:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
         </is>
       </c>
     </row>
@@ -1995,8 +2329,10 @@
       <c r="D49" t="n">
         <v>6.5</v>
       </c>
-      <c r="E49" t="n">
-        <v>3.1</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2006,6 +2342,11 @@
       <c r="G49" t="inlineStr">
         <is>
           <t>cpe:2.3:a:tp-link:tapo:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
         </is>
       </c>
     </row>
@@ -2028,8 +2369,10 @@
       <c r="D50" t="n">
         <v>7.5</v>
       </c>
-      <c r="E50" t="n">
-        <v>3.1</v>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2039,6 +2382,11 @@
       <c r="G50" t="inlineStr">
         <is>
           <t>cpe:2.3:a:tp-link:tapo:*:*:*:*:*:android:*:*|cpe:2.3:h:tp-link:tapo_c200:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
         </is>
       </c>
     </row>
@@ -2061,8 +2409,10 @@
       <c r="D51" t="n">
         <v>5.7</v>
       </c>
-      <c r="E51" t="n">
-        <v>3.1</v>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2072,6 +2422,11 @@
       <c r="G51" t="inlineStr">
         <is>
           <t>cpe:2.3:o:meross:msh30q_firmware:4.5.23:*:*:*:*:*:*:*|cpe:2.3:h:meross:msh30q:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>meross</t>
         </is>
       </c>
     </row>
@@ -2094,8 +2449,10 @@
       <c r="D52" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E52" t="n">
-        <v>3.1</v>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2105,6 +2462,11 @@
       <c r="G52" t="inlineStr">
         <is>
           <t>cpe:2.3:o:meross:msh30q_firmware:4.5.23:*:*:*:*:*:*:*|cpe:2.3:h:meross:msh30q:-:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>meross</t>
         </is>
       </c>
     </row>
@@ -2129,8 +2491,10 @@
       <c r="D53" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E53" t="n">
-        <v>3</v>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2140,6 +2504,11 @@
       <c r="G53" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tapo_c210_firmware:1.3.0:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_c210:v2:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
         </is>
       </c>
     </row>
@@ -2164,8 +2533,10 @@
       <c r="D54" t="n">
         <v>8</v>
       </c>
-      <c r="E54" t="n">
-        <v>3.1</v>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2175,6 +2546,11 @@
       <c r="G54" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tapo_c210_firmware:1.3.0:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_c210:v2:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
         </is>
       </c>
     </row>
@@ -2197,8 +2573,10 @@
       <c r="D55" t="n">
         <v>4.8</v>
       </c>
-      <c r="E55" t="n">
-        <v>3.1</v>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2206,6 +2584,11 @@
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2226,8 +2609,10 @@
       <c r="D56" t="n">
         <v>8</v>
       </c>
-      <c r="E56" t="n">
-        <v>3.1</v>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2237,6 +2622,11 @@
       <c r="G56" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tl-wpa8630_firmware:2.0.4:build_20230427:*:*:*:*:*:*|cpe:2.3:h:tp-link:tl-wpa8630:2.0:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>tplink</t>
         </is>
       </c>
     </row>
@@ -2264,6 +2654,11 @@
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2289,6 +2684,11 @@
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2309,8 +2709,10 @@
       <c r="D59" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E59" t="n">
-        <v>3.1</v>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2320,6 +2722,11 @@
       <c r="G59" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tapo_h100_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_h100:1.0:*:*:*:*:*:*:*|cpe:2.3:o:tp-link:tapo_p100_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_p100:1.0:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
         </is>
       </c>
     </row>
@@ -2343,8 +2750,10 @@
       <c r="D60" t="n">
         <v>7.8</v>
       </c>
-      <c r="E60" t="n">
-        <v>3.1</v>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2354,6 +2763,11 @@
       <c r="G60" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tapo_c260_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_c260:1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
         </is>
       </c>
     </row>
@@ -2376,8 +2790,10 @@
       <c r="D61" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E61" t="n">
-        <v>3.1</v>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2387,6 +2803,11 @@
       <c r="G61" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tapo_c260_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_c260:1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
         </is>
       </c>
     </row>
@@ -2409,8 +2830,10 @@
       <c r="D62" t="n">
         <v>6.5</v>
       </c>
-      <c r="E62" t="n">
-        <v>3.1</v>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2420,6 +2843,11 @@
       <c r="G62" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tapo_c260_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_c260:1:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
         </is>
       </c>
     </row>
@@ -2447,8 +2875,10 @@
       <c r="D63" t="n">
         <v>6.5</v>
       </c>
-      <c r="E63" t="n">
-        <v>3.1</v>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2458,6 +2888,11 @@
       <c r="G63" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tapo_c520ws_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_c520ws:2.6:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
         </is>
       </c>
     </row>
@@ -2488,8 +2923,10 @@
       <c r="D64" t="n">
         <v>6.5</v>
       </c>
-      <c r="E64" t="n">
-        <v>3.1</v>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2499,6 +2936,11 @@
       <c r="G64" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tapo_c520ws_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_c520ws:2.6:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
         </is>
       </c>
     </row>
@@ -2527,8 +2969,10 @@
       <c r="D65" t="n">
         <v>6.5</v>
       </c>
-      <c r="E65" t="n">
-        <v>3.1</v>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2538,6 +2982,11 @@
       <c r="G65" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tapo_c520ws_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_c520ws:2.6:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
         </is>
       </c>
     </row>
@@ -2561,8 +3010,10 @@
       <c r="D66" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E66" t="n">
-        <v>3.1</v>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2572,6 +3023,11 @@
       <c r="G66" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tapo_c520ws_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_c520ws:2.6:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
         </is>
       </c>
     </row>
@@ -2595,8 +3051,10 @@
       <c r="D67" t="n">
         <v>6.5</v>
       </c>
-      <c r="E67" t="n">
-        <v>3.1</v>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2606,6 +3064,11 @@
       <c r="G67" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tapo_c520ws_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_c520ws:2.6:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
         </is>
       </c>
     </row>
@@ -2628,8 +3091,10 @@
       <c r="D68" t="n">
         <v>6.5</v>
       </c>
-      <c r="E68" t="n">
-        <v>3.1</v>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2639,6 +3104,11 @@
       <c r="G68" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tapo_c520ws_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_c520ws:2.6:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
         </is>
       </c>
     </row>
@@ -2662,8 +3132,10 @@
       <c r="D69" t="n">
         <v>6.5</v>
       </c>
-      <c r="E69" t="n">
-        <v>3.1</v>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2673,6 +3145,11 @@
       <c r="G69" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tapo_c200_firmware:1.0.5:build_240327:*:*:*:*:*:*|cpe:2.3:o:tp-link:tapo_c200_firmware:1.0.12:build_240527:*:*:*:*:*:*|cpe:2.3:o:tp-link:tapo_c200_firmware:1.0.13:build_240619:*:*:*:*:*:*|cpe:2.3:o:tp-link:tapo_c200_firmware:1.0.17:build_240806:*:*:*:*:*:*|cpe:2.3:o:tp-link:tapo_c200_firmware:1.1.4:build_241219:*:*:*:*:*:*|cpe:2.3:o:tp-link:tapo_c200_firmware:1.1.8:build_250310:*:*:*:*:*:*|cpe:2.3:o:tp-link:tapo_c200_firmware:1.2.3:build_250610:*:*:*:*:*:*|cpe:2.3:o:tp-link:tapo_c200_firmware:1.3.1:build_250910:*:*:*:*:*:*|cpe:2.3:o:tp-link:tapo_c200_firmware:1.3.3:build_251119:*:*:*:*:*:*|cpe:2.3:o:tp-link:tapo_c200_firmware:1.3.5:build_260228:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_c200:5:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
         </is>
       </c>
     </row>
@@ -2701,8 +3178,10 @@
       <c r="D70" t="n">
         <v>6.5</v>
       </c>
-      <c r="E70" t="n">
-        <v>3.1</v>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2712,6 +3191,11 @@
       <c r="G70" t="inlineStr">
         <is>
           <t>cpe:2.3:o:tp-link:tapo_c520ws_firmware:*:*:*:*:*:*:*:*|cpe:2.3:h:tp-link:tapo_c520ws:2.0:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>tp-link tapo</t>
         </is>
       </c>
     </row>
@@ -2742,8 +3226,10 @@
       <c r="D71" t="n">
         <v>5.5</v>
       </c>
-      <c r="E71" t="n">
-        <v>3.1</v>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2753,6 +3239,11 @@
       <c r="G71" t="inlineStr">
         <is>
           <t>cpe:2.3:o:linux:linux_kernel:*:*:*:*:*:*:*:*</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>tplink</t>
         </is>
       </c>
     </row>
